--- a/Datos limpios/Pricing diario/2025/Total.xlsx
+++ b/Datos limpios/Pricing diario/2025/Total.xlsx
@@ -8128,298 +8128,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D6CA5EAACE9DA04D9E421A617A76D009" ma:contentTypeVersion="19" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="854b0670eee28d8fa271d4f22cb9c97d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77131357-5c03-45fa-a80b-b9111bb46cb1" xmlns:ns3="d3f11db4-a96c-41b4-b8ec-902c72f52048" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b486ba09ce8a2fb19cc660d7edf32df4" ns2:_="" ns3:_="">
-    <xsd:import namespace="77131357-5c03-45fa-a80b-b9111bb46cb1"/>
-    <xsd:import namespace="d3f11db4-a96c-41b4-b8ec-902c72f52048"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="77131357-5c03-45fa-a80b-b9111bb46cb1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="20" nillable="true" ma:displayName="Estado de aprobación" ma:internalName="Estado_x0020_de_x0020_aprobaci_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6ab20cb4-9c0f-41d2-89f3-02c382a657d6" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d3f11db4-a96c-41b4-b8ec-902c72f52048" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="24" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ac6aff7b-77d9-4645-af3f-7b0008d975fa}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d3f11db4-a96c-41b4-b8ec-902c72f52048">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1" xsi:nil="true"/>
-    <TaxCatchAll xmlns="d3f11db4-a96c-41b4-b8ec-902c72f52048" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4C8187F-1E76-428B-867B-B2A3E366EE2C}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154628FF-87C1-45D0-B955-CDA26DF2006C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2901503D-8277-4ADE-B445-1E09125BC271}"/>
 </file>
--- a/Datos limpios/Pricing diario/2025/Total.xlsx
+++ b/Datos limpios/Pricing diario/2025/Total.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H298"/>
+  <dimension ref="A1:H323"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -6897,10 +6897,10 @@
         <v>5645.639999999999</v>
       </c>
       <c r="G251">
-        <v>73682.87999999999</v>
+        <v>73542.2</v>
       </c>
       <c r="H251">
-        <v>410059.26</v>
+        <v>409918.58</v>
       </c>
     </row>
     <row r="252">
@@ -7105,10 +7105,10 @@
         <v>3401.69</v>
       </c>
       <c r="G259">
-        <v>164194.48</v>
+        <v>164160.56</v>
       </c>
       <c r="H259">
-        <v>438744.4300000001</v>
+        <v>438710.51</v>
       </c>
     </row>
     <row r="260">
@@ -7229,7 +7229,7 @@
         <v>72983.32000000001</v>
       </c>
       <c r="E264">
-        <v>481877.8100000001</v>
+        <v>480607.55</v>
       </c>
       <c r="F264">
         <v>3468.49</v>
@@ -7238,7 +7238,7 @@
         <v>100670.96</v>
       </c>
       <c r="H264">
-        <v>665943.84</v>
+        <v>664673.58</v>
       </c>
     </row>
     <row r="265">
@@ -7261,10 +7261,10 @@
         <v>563.99</v>
       </c>
       <c r="G265">
-        <v>162646.26</v>
+        <v>162458.53</v>
       </c>
       <c r="H265">
-        <v>1706993.91</v>
+        <v>1706806.18</v>
       </c>
     </row>
     <row r="266">
@@ -7281,16 +7281,16 @@
         <v>206389.3</v>
       </c>
       <c r="E266">
-        <v>1574424.4</v>
+        <v>1574405.94</v>
       </c>
       <c r="F266">
         <v>1872.14</v>
       </c>
       <c r="G266">
-        <v>161099.2</v>
+        <v>160099.2</v>
       </c>
       <c r="H266">
-        <v>2042044.69</v>
+        <v>2041026.23</v>
       </c>
     </row>
     <row r="267">
@@ -7307,7 +7307,7 @@
         <v>152926.75</v>
       </c>
       <c r="E267">
-        <v>837417.1100000001</v>
+        <v>837359.4</v>
       </c>
       <c r="F267">
         <v>5454.65</v>
@@ -7316,7 +7316,7 @@
         <v>106359.36</v>
       </c>
       <c r="H267">
-        <v>1144108.5</v>
+        <v>1144050.79</v>
       </c>
     </row>
     <row r="268">
@@ -7463,16 +7463,16 @@
         <v>70085.70999999999</v>
       </c>
       <c r="E273">
-        <v>380373.22</v>
+        <v>380369.38</v>
       </c>
       <c r="F273">
         <v>11864.14</v>
       </c>
       <c r="G273">
-        <v>59917.52</v>
+        <v>59796.03</v>
       </c>
       <c r="H273">
-        <v>556041.9</v>
+        <v>555916.5700000001</v>
       </c>
     </row>
     <row r="274">
@@ -7489,7 +7489,7 @@
         <v>92329.42</v>
       </c>
       <c r="E274">
-        <v>370912.65</v>
+        <v>370765.3</v>
       </c>
       <c r="F274">
         <v>1132.62</v>
@@ -7498,7 +7498,7 @@
         <v>69660.97</v>
       </c>
       <c r="H274">
-        <v>557229.26</v>
+        <v>557081.91</v>
       </c>
     </row>
     <row r="275">
@@ -7515,16 +7515,16 @@
         <v>90230.02000000002</v>
       </c>
       <c r="E275">
-        <v>423023.69</v>
+        <v>423024.43</v>
       </c>
       <c r="F275">
         <v>12823.31</v>
       </c>
       <c r="G275">
-        <v>70228.18000000001</v>
+        <v>69938.09000000001</v>
       </c>
       <c r="H275">
-        <v>660036.8800000001</v>
+        <v>659747.53</v>
       </c>
     </row>
     <row r="276">
@@ -7593,7 +7593,7 @@
         <v>97668.79000000001</v>
       </c>
       <c r="E278">
-        <v>227120.04</v>
+        <v>227000.04</v>
       </c>
       <c r="F278">
         <v>1361.07</v>
@@ -7602,7 +7602,7 @@
         <v>83410.52</v>
       </c>
       <c r="H278">
-        <v>427881.6800000001</v>
+        <v>427761.6800000001</v>
       </c>
     </row>
     <row r="279">
@@ -7625,10 +7625,10 @@
         <v>994.22</v>
       </c>
       <c r="G279">
-        <v>87765.79000000001</v>
+        <v>87610.52</v>
       </c>
       <c r="H279">
-        <v>420817.7</v>
+        <v>420662.43</v>
       </c>
     </row>
     <row r="280">
@@ -7781,10 +7781,10 @@
         <v>901.3099999999999</v>
       </c>
       <c r="G285">
-        <v>137133.03</v>
+        <v>136836.47</v>
       </c>
       <c r="H285">
-        <v>324046.59</v>
+        <v>323750.03</v>
       </c>
     </row>
     <row r="286">
@@ -7882,13 +7882,13 @@
         <v>106043.07</v>
       </c>
       <c r="F289">
-        <v>18464.95</v>
+        <v>17464.95</v>
       </c>
       <c r="G289">
         <v>107090.62</v>
       </c>
       <c r="H289">
-        <v>408688.26</v>
+        <v>407688.26</v>
       </c>
     </row>
     <row r="290">
@@ -8104,25 +8104,675 @@
         <v>45957</v>
       </c>
       <c r="B298">
-        <v>7950</v>
+        <v>19388.34</v>
       </c>
       <c r="C298">
-        <v>950</v>
+        <v>18330.34</v>
       </c>
       <c r="D298">
-        <v>1510</v>
+        <v>64599.99000000001</v>
       </c>
       <c r="E298">
-        <v>2677.84</v>
+        <v>56853.16</v>
       </c>
       <c r="F298">
-        <v>0</v>
+        <v>1289.08</v>
       </c>
       <c r="G298">
-        <v>960</v>
+        <v>50675.54</v>
       </c>
       <c r="H298">
-        <v>14047.84</v>
+        <v>211136.45</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B299">
+        <v>18221.26</v>
+      </c>
+      <c r="C299">
+        <v>11008.73</v>
+      </c>
+      <c r="D299">
+        <v>117118.26</v>
+      </c>
+      <c r="E299">
+        <v>118743.84</v>
+      </c>
+      <c r="F299">
+        <v>1556.12</v>
+      </c>
+      <c r="G299">
+        <v>102356.76</v>
+      </c>
+      <c r="H299">
+        <v>369004.97</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B300">
+        <v>11773</v>
+      </c>
+      <c r="C300">
+        <v>10770.94</v>
+      </c>
+      <c r="D300">
+        <v>95470.38</v>
+      </c>
+      <c r="E300">
+        <v>58551.82</v>
+      </c>
+      <c r="F300">
+        <v>1664.4</v>
+      </c>
+      <c r="G300">
+        <v>62442.2</v>
+      </c>
+      <c r="H300">
+        <v>240672.74</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B301">
+        <v>21536.23</v>
+      </c>
+      <c r="C301">
+        <v>11518.56</v>
+      </c>
+      <c r="D301">
+        <v>130203.01</v>
+      </c>
+      <c r="E301">
+        <v>55796.11</v>
+      </c>
+      <c r="F301">
+        <v>892.0599999999999</v>
+      </c>
+      <c r="G301">
+        <v>92197.7</v>
+      </c>
+      <c r="H301">
+        <v>312143.67</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B302">
+        <v>31360</v>
+      </c>
+      <c r="C302">
+        <v>8032.99</v>
+      </c>
+      <c r="D302">
+        <v>146743.22</v>
+      </c>
+      <c r="E302">
+        <v>48408.11</v>
+      </c>
+      <c r="F302">
+        <v>7660.339999999999</v>
+      </c>
+      <c r="G302">
+        <v>90562.22000000002</v>
+      </c>
+      <c r="H302">
+        <v>332766.88</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>159.87</v>
+      </c>
+      <c r="E303">
+        <v>2215.14</v>
+      </c>
+      <c r="F303">
+        <v>0</v>
+      </c>
+      <c r="G303">
+        <v>1597.81</v>
+      </c>
+      <c r="H303">
+        <v>3972.82</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2">
+        <v>45963</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>0</v>
+      </c>
+      <c r="E304">
+        <v>13081.43</v>
+      </c>
+      <c r="F304">
+        <v>0</v>
+      </c>
+      <c r="G304">
+        <v>0</v>
+      </c>
+      <c r="H304">
+        <v>13081.43</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B305">
+        <v>26455.8</v>
+      </c>
+      <c r="C305">
+        <v>8996.65</v>
+      </c>
+      <c r="D305">
+        <v>137256.09</v>
+      </c>
+      <c r="E305">
+        <v>81738.89999999999</v>
+      </c>
+      <c r="F305">
+        <v>2699.28</v>
+      </c>
+      <c r="G305">
+        <v>99453.11</v>
+      </c>
+      <c r="H305">
+        <v>356599.83</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B306">
+        <v>41360.75999999999</v>
+      </c>
+      <c r="C306">
+        <v>31218.63</v>
+      </c>
+      <c r="D306">
+        <v>100755.44</v>
+      </c>
+      <c r="E306">
+        <v>107688.57</v>
+      </c>
+      <c r="F306">
+        <v>1710.15</v>
+      </c>
+      <c r="G306">
+        <v>77600.31999999999</v>
+      </c>
+      <c r="H306">
+        <v>360333.8700000001</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B307">
+        <v>20673.65</v>
+      </c>
+      <c r="C307">
+        <v>22130.88</v>
+      </c>
+      <c r="D307">
+        <v>295755.66</v>
+      </c>
+      <c r="E307">
+        <v>42870.54</v>
+      </c>
+      <c r="F307">
+        <v>4628.26</v>
+      </c>
+      <c r="G307">
+        <v>95292.70000000001</v>
+      </c>
+      <c r="H307">
+        <v>481351.6900000001</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B308">
+        <v>12292.76</v>
+      </c>
+      <c r="C308">
+        <v>-5764.84</v>
+      </c>
+      <c r="D308">
+        <v>212826.47</v>
+      </c>
+      <c r="E308">
+        <v>111236.27</v>
+      </c>
+      <c r="F308">
+        <v>1946.28</v>
+      </c>
+      <c r="G308">
+        <v>71152.63</v>
+      </c>
+      <c r="H308">
+        <v>403689.57</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B309">
+        <v>23785.06</v>
+      </c>
+      <c r="C309">
+        <v>9313.780000000001</v>
+      </c>
+      <c r="D309">
+        <v>127060.58</v>
+      </c>
+      <c r="E309">
+        <v>127863.62</v>
+      </c>
+      <c r="F309">
+        <v>2209.08</v>
+      </c>
+      <c r="G309">
+        <v>61774.31</v>
+      </c>
+      <c r="H309">
+        <v>352006.43</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2">
+        <v>45969</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+      <c r="C310">
+        <v>15</v>
+      </c>
+      <c r="D310">
+        <v>516.72</v>
+      </c>
+      <c r="E310">
+        <v>1378.62</v>
+      </c>
+      <c r="F310">
+        <v>0</v>
+      </c>
+      <c r="G310">
+        <v>254.2</v>
+      </c>
+      <c r="H310">
+        <v>2164.54</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2">
+        <v>45970</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>35</v>
+      </c>
+      <c r="E311">
+        <v>500</v>
+      </c>
+      <c r="F311">
+        <v>0</v>
+      </c>
+      <c r="G311">
+        <v>0</v>
+      </c>
+      <c r="H311">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B312">
+        <v>14799.99</v>
+      </c>
+      <c r="C312">
+        <v>8460.230000000001</v>
+      </c>
+      <c r="D312">
+        <v>147347.01</v>
+      </c>
+      <c r="E312">
+        <v>51602.62</v>
+      </c>
+      <c r="F312">
+        <v>2021.14</v>
+      </c>
+      <c r="G312">
+        <v>92511.98000000001</v>
+      </c>
+      <c r="H312">
+        <v>316742.97</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B313">
+        <v>22060.6</v>
+      </c>
+      <c r="C313">
+        <v>15913.23</v>
+      </c>
+      <c r="D313">
+        <v>187223.45</v>
+      </c>
+      <c r="E313">
+        <v>68845.47</v>
+      </c>
+      <c r="F313">
+        <v>1437.55</v>
+      </c>
+      <c r="G313">
+        <v>92712.08</v>
+      </c>
+      <c r="H313">
+        <v>388192.38</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B314">
+        <v>10481.56</v>
+      </c>
+      <c r="C314">
+        <v>11562.86</v>
+      </c>
+      <c r="D314">
+        <v>122982.8</v>
+      </c>
+      <c r="E314">
+        <v>85335.42000000001</v>
+      </c>
+      <c r="F314">
+        <v>1078.46</v>
+      </c>
+      <c r="G314">
+        <v>109947.54</v>
+      </c>
+      <c r="H314">
+        <v>341388.64</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B315">
+        <v>15739.25</v>
+      </c>
+      <c r="C315">
+        <v>9993.230000000001</v>
+      </c>
+      <c r="D315">
+        <v>195224.96</v>
+      </c>
+      <c r="E315">
+        <v>75975.76999999999</v>
+      </c>
+      <c r="F315">
+        <v>1881.48</v>
+      </c>
+      <c r="G315">
+        <v>145746.27</v>
+      </c>
+      <c r="H315">
+        <v>444560.96</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B316">
+        <v>14622.57</v>
+      </c>
+      <c r="C316">
+        <v>10007.08</v>
+      </c>
+      <c r="D316">
+        <v>359640.37</v>
+      </c>
+      <c r="E316">
+        <v>51099.35</v>
+      </c>
+      <c r="F316">
+        <v>1177.15</v>
+      </c>
+      <c r="G316">
+        <v>159314.17</v>
+      </c>
+      <c r="H316">
+        <v>595860.6900000001</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2">
+        <v>45976</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>1776.47</v>
+      </c>
+      <c r="E317">
+        <v>180</v>
+      </c>
+      <c r="F317">
+        <v>145</v>
+      </c>
+      <c r="G317">
+        <v>720</v>
+      </c>
+      <c r="H317">
+        <v>2821.47</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2">
+        <v>45977</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>800.28</v>
+      </c>
+      <c r="D318">
+        <v>0</v>
+      </c>
+      <c r="E318">
+        <v>500</v>
+      </c>
+      <c r="F318">
+        <v>0</v>
+      </c>
+      <c r="G318">
+        <v>0</v>
+      </c>
+      <c r="H318">
+        <v>1300.28</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B319">
+        <v>31748.74</v>
+      </c>
+      <c r="C319">
+        <v>8849.66</v>
+      </c>
+      <c r="D319">
+        <v>113945.08</v>
+      </c>
+      <c r="E319">
+        <v>74008.22</v>
+      </c>
+      <c r="F319">
+        <v>743.95</v>
+      </c>
+      <c r="G319">
+        <v>113416.33</v>
+      </c>
+      <c r="H319">
+        <v>342711.98</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B320">
+        <v>27423.37</v>
+      </c>
+      <c r="C320">
+        <v>6666.099999999999</v>
+      </c>
+      <c r="D320">
+        <v>80879.83</v>
+      </c>
+      <c r="E320">
+        <v>102518.02</v>
+      </c>
+      <c r="F320">
+        <v>480</v>
+      </c>
+      <c r="G320">
+        <v>116519.79</v>
+      </c>
+      <c r="H320">
+        <v>334487.11</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B321">
+        <v>27056</v>
+      </c>
+      <c r="C321">
+        <v>15932.94</v>
+      </c>
+      <c r="D321">
+        <v>113818.39</v>
+      </c>
+      <c r="E321">
+        <v>97366.82999999999</v>
+      </c>
+      <c r="F321">
+        <v>462.46</v>
+      </c>
+      <c r="G321">
+        <v>136266.54</v>
+      </c>
+      <c r="H321">
+        <v>390903.16</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B322">
+        <v>29415.74</v>
+      </c>
+      <c r="C322">
+        <v>9690.279999999999</v>
+      </c>
+      <c r="D322">
+        <v>68768.36</v>
+      </c>
+      <c r="E322">
+        <v>66451.56</v>
+      </c>
+      <c r="F322">
+        <v>2027.73</v>
+      </c>
+      <c r="G322">
+        <v>100749.12</v>
+      </c>
+      <c r="H322">
+        <v>277102.79</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B323">
+        <v>10210</v>
+      </c>
+      <c r="C323">
+        <v>2256.3</v>
+      </c>
+      <c r="D323">
+        <v>7049.309999999999</v>
+      </c>
+      <c r="E323">
+        <v>11084.31</v>
+      </c>
+      <c r="F323">
+        <v>0</v>
+      </c>
+      <c r="G323">
+        <v>20391.37</v>
+      </c>
+      <c r="H323">
+        <v>50991.29</v>
       </c>
     </row>
   </sheetData>
